--- a/tools/importer/reports/import-form-fragment.report.xlsx
+++ b/tools/importer/reports/import-form-fragment.report.xlsx
@@ -52,7 +52,7 @@
     <t>homepage</t>
   </si>
   <si>
-    <t>2026-07-21T17:34:47.654Z</t>
+    <t>2026-07-21T19:11:20.224Z</t>
   </si>
   <si>
     <t>Power Confident Business Decisions | Dun &amp; Bradstreet</t>
@@ -73,7 +73,7 @@
     <t>form-fragment</t>
   </si>
   <si>
-    <t>2026-07-21T19:09:35.578Z</t>
+    <t>2026-07-21T20:27:49.089Z</t>
   </si>
   <si>
     <t>Schedule a Strategy Session</t>
